--- a/CPRD Raw Analysis/Results/Cohort/Output_gt_overall_healthcare_roles_count_SOURCE.xlsx
+++ b/CPRD Raw Analysis/Results/Cohort/Output_gt_overall_healthcare_roles_count_SOURCE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B147"/>
+  <dimension ref="A1:B152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -376,1514 +376,1514 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Administrative Non-clinical</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>368,133 (40.8%)</t>
+          <t>361,678 (40.1%)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>General Practitioner</t>
+          <t>GP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>361,781 (40.1%)</t>
+          <t>361,493 (40.1%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nurse</t>
+          <t>Non-registered other</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87,655 (9.7%)</t>
+          <t>122,532 (13.6%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Nurse</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>83,966 (9.3%)</t>
+          <t>44,904 (5.0%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>__Healthcare Provider Roles__</t>
+          <t>AHP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>7,405 (0.8%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>General Medical Practitioner</t>
+          <t>Medic non-GP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>303,981 (33.7%)</t>
+          <t>3,122 (0.3%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Receptionist</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>90,210 (10.0%)</t>
+          <t>334 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Manager</t>
+          <t>Social</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>73,922 (8.2%)</t>
+          <t>34 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>System Administrator</t>
+          <t>Dental</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>48,268 (5.4%)</t>
+          <t>33 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Clerical Worker</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>46,096 (5.1%)</t>
+          <t>__Healthcare Provider Roles__</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Community Practitioner</t>
+          <t>General Medical Practitioner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>43,287 (4.8%)</t>
+          <t>303,981 (33.7%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Health Care Support Worker</t>
+          <t>Receptionist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>37,858 (4.2%)</t>
+          <t>90,210 (10.0%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Salaried General Practitioner</t>
+          <t>Manager</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26,363 (2.9%)</t>
+          <t>73,922 (8.2%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Healthcare Assistant</t>
+          <t>System Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>25,945 (2.9%)</t>
+          <t>48,268 (5.4%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Community Administrator</t>
+          <t>Clerical Worker</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22,350 (2.5%)</t>
+          <t>46,096 (5.1%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Desktop Support Administrator</t>
+          <t>Community Practitioner</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21,074 (2.3%)</t>
+          <t>43,287 (4.8%)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Administrator</t>
+          <t>Health Care Support Worker</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>16,046 (1.8%)</t>
+          <t>37,858 (4.2%)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Community Nurse</t>
+          <t>Salaried General Practitioner</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15,343 (1.7%)</t>
+          <t>26,363 (2.9%)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Medical Secretary</t>
+          <t>Healthcare Assistant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14,165 (1.6%)</t>
+          <t>25,945 (2.9%)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sessional GP</t>
+          <t>Community Administrator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>12,341 (1.4%)</t>
+          <t>22,350 (2.5%)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Secretary</t>
+          <t>Desktop Support Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>12,271 (1.4%)</t>
+          <t>21,074 (2.3%)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Specialist Nurse Practitioner</t>
+          <t>Senior Administrator</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>11,985 (1.3%)</t>
+          <t>16,046 (1.8%)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GP Registrar</t>
+          <t>Community Nurse</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11,921 (1.3%)</t>
+          <t>15,343 (1.7%)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Staff Nurse</t>
+          <t>Medical Secretary</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7,071 (0.8%)</t>
+          <t>14,165 (1.6%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Phlebotomist</t>
+          <t>Sessional GP</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6,052 (0.7%)</t>
+          <t>12,341 (1.4%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Pharmacist</t>
+          <t>Secretary</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5,510 (0.6%)</t>
+          <t>12,271 (1.4%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Dispenser</t>
+          <t>Specialist Nurse Practitioner</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5,292 (0.6%)</t>
+          <t>11,985 (1.3%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Locum GP</t>
+          <t>GP Registrar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4,765 (0.5%)</t>
+          <t>11,921 (1.3%)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Clinical Coder</t>
+          <t>Staff Nurse</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3,942 (0.4%)</t>
+          <t>7,071 (0.8%)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Manager</t>
+          <t>Phlebotomist</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>3,567 (0.4%)</t>
+          <t>6,052 (0.7%)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sister/Charge Nurse</t>
+          <t>Pharmacist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2,480 (0.3%)</t>
+          <t>5,510 (0.6%)</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Practitioner - General Practitioner</t>
+          <t>Dispenser</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2,122 (0.2%)</t>
+          <t>5,292 (0.6%)</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Nurse Manager</t>
+          <t>Locum GP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2,122 (0.2%)</t>
+          <t>4,765 (0.5%)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Consultant</t>
+          <t>Clinical Coder</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2,046 (0.2%)</t>
+          <t>3,942 (0.4%)</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Associate Practitioner - Nurse</t>
+          <t>Senior Manager</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1,950 (0.2%)</t>
+          <t>3,567 (0.4%)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Appointments Clerk</t>
+          <t>Sister/Charge Nurse</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1,649 (0.2%)</t>
+          <t>2,480 (0.3%)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Enrolled Nurse</t>
+          <t>Associate Practitioner - General Practitioner</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1,590 (0.2%)</t>
+          <t>2,122 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Nurse Consultant</t>
+          <t>Nurse Manager</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1,580 (0.2%)</t>
+          <t>2,122 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Technician - Admin &amp; Clerical</t>
+          <t>Consultant</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1,226 (0.1%)</t>
+          <t>2,046 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Helpdesk Administrator</t>
+          <t>Associate Practitioner - Nurse</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1,059 (0.1%)</t>
+          <t>1,950 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>System Worker</t>
+          <t>Appointments Clerk</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1,032 (0.1%)</t>
+          <t>1,649 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Desktop Support Technician</t>
+          <t>Enrolled Nurse</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>938 (0.1%)</t>
+          <t>1,590 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Medical Records Clerk</t>
+          <t>Nurse Consultant</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>918 (0.1%)</t>
+          <t>1,580 (0.2%)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Medical Technical Officer - Pharmacy</t>
+          <t>Technician - Admin &amp; Clerical</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>837 (0.1%)</t>
+          <t>1,226 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Network Administrator</t>
+          <t>Helpdesk Administrator</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>616 (0.1%)</t>
+          <t>1,059 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clinical Application Administrator</t>
+          <t>System Worker</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>606 (0.1%)</t>
+          <t>1,032 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Admin Clerk</t>
+          <t>Desktop Support Technician</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>576 (0.1%)</t>
+          <t>938 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Clinical Assistant</t>
+          <t>Medical Records Clerk</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>542 (0.1%)</t>
+          <t>918 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Health Records Administrator</t>
+          <t>Medical Technical Officer - Pharmacy</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>509 (0.1%)</t>
+          <t>837 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Physiotherapist</t>
+          <t>Network Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>474 (0.1%)</t>
+          <t>616 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Assistant Practitioner</t>
+          <t>Clinical Application Administrator</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>450 (0.0%)</t>
+          <t>606 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Health Records Clerk</t>
+          <t>Other Community Health Service - Admin Clerk</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>381 (0.0%)</t>
+          <t>576 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Other Community Health Service</t>
+          <t>Clinical Assistant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>334 (0.0%)</t>
+          <t>542 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Network Technician</t>
+          <t>Health Records Administrator</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>304 (0.0%)</t>
+          <t>509 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Associate Practitioner</t>
+          <t>Physiotherapist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>294 (0.0%)</t>
+          <t>474 (0.1%)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Practitioner</t>
+          <t>Assistant Practitioner</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>288 (0.0%)</t>
+          <t>450 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Information Officer</t>
+          <t>Health Records Clerk</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>285 (0.0%)</t>
+          <t>381 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Medical Records Manager</t>
+          <t>Other Community Health Service</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>280 (0.0%)</t>
+          <t>334 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Advanced Practitioner</t>
+          <t>Network Technician</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>267 (0.0%)</t>
+          <t>304 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Medical Student</t>
+          <t>Associate Practitioner</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>226 (0.0%)</t>
+          <t>294 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Paramedic Specialist Practitioner</t>
+          <t>Practitioner</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>217 (0.0%)</t>
+          <t>288 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Modern Matron</t>
+          <t>Information Officer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>212 (0.0%)</t>
+          <t>285 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Paramedic</t>
+          <t>Medical Records Manager</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>211 (0.0%)</t>
+          <t>280 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Helpdesk Technician</t>
+          <t>Advanced Practitioner</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>204 (0.0%)</t>
+          <t>267 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Paramedic Manager</t>
+          <t>Medical Student</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>198 (0.0%)</t>
+          <t>226 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Associate Specialist</t>
+          <t>Paramedic Specialist Practitioner</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>192 (0.0%)</t>
+          <t>217 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Deputising Doctor</t>
+          <t>Modern Matron</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>174 (0.0%)</t>
+          <t>212 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Officer</t>
+          <t>Paramedic</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>163 (0.0%)</t>
+          <t>211 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Staff Grade</t>
+          <t>Helpdesk Technician</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>161 (0.0%)</t>
+          <t>204 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Specialist Practitioner</t>
+          <t>Paramedic Manager</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>135 (0.0%)</t>
+          <t>198 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Counsellor</t>
+          <t>Associate Specialist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>128 (0.0%)</t>
+          <t>192 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Helper/Assistant</t>
+          <t>Deputising Doctor</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>127 (0.0%)</t>
+          <t>174 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Assistant GP</t>
+          <t>Officer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>125 (0.0%)</t>
+          <t>163 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>House Officer - Post Registration</t>
+          <t>Staff Grade</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>113 (0.0%)</t>
+          <t>161 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Caldicott Guardian</t>
+          <t>Specialist Practitioner</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>112 (0.0%)</t>
+          <t>135 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist</t>
+          <t>Counsellor</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>111 (0.0%)</t>
+          <t>128 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Community Mental Health Nurse</t>
+          <t>Helper/Assistant</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>90 (0.0%)</t>
+          <t>127 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Clinical Director - Medical</t>
+          <t>Assistant GP</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>89 (0.0%)</t>
+          <t>125 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Dietitian</t>
+          <t>House Officer - Post Registration</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>79 (0.0%)</t>
+          <t>113 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Osteopath</t>
+          <t>Caldicott Guardian</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>77 (0.0%)</t>
+          <t>112 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analyst</t>
+          <t>Chiropodist/Podiatrist</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>75 (0.0%)</t>
+          <t>111 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Medical Technical Officer</t>
+          <t>Community Mental Health Nurse</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>67 (0.0%)</t>
+          <t>90 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Therapist</t>
+          <t>Clinical Director - Medical</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>51 (0.0%)</t>
+          <t>89 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Art Therapist</t>
+          <t>Dietitian</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>50 (0.0%)</t>
+          <t>79 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Radiologist</t>
+          <t>Osteopath</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>49 (0.0%)</t>
+          <t>77 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Trainee Practitioner</t>
+          <t>Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>46 (0.0%)</t>
+          <t>75 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Physiotherapist Manager</t>
+          <t>Medical Technical Officer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>43 (0.0%)</t>
+          <t>67 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Availability Monitor</t>
+          <t>Therapist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>35 (0.0%)</t>
+          <t>51 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Regional Dental Officer</t>
+          <t>Art Therapist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>33 (0.0%)</t>
+          <t>50 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Art Therapist Manager</t>
+          <t>Radiologist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>32 (0.0%)</t>
+          <t>49 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Student Practice Nurse</t>
+          <t>Trainee Practitioner</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>32 (0.0%)</t>
+          <t>46 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Radiographer</t>
+          <t>Physiotherapist Manager</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>28 (0.0%)</t>
+          <t>43 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior House Officer</t>
+          <t>Availability Monitor</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>28 (0.0%)</t>
+          <t>35 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Finance Director</t>
+          <t>Regional Dental Officer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>26 (0.0%)</t>
+          <t>33 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Researcher</t>
+          <t>Art Therapist Manager</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>25 (0.0%)</t>
+          <t>32 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Hospital Practitioner</t>
+          <t>Student Practice Nurse</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>24 (0.0%)</t>
+          <t>32 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Physiotherapist Specialist Practitioner</t>
+          <t>Radiographer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>24 (0.0%)</t>
+          <t>28 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Intermediate Care staff</t>
+          <t>Senior House Officer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>23 (0.0%)</t>
+          <t>28 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Child Protection worker</t>
+          <t>Finance Director</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>22 (0.0%)</t>
+          <t>26 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Call Operator</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>21 (0.0%)</t>
+          <t>25 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Physician Assistant</t>
+          <t>Hospital Practitioner</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>21 (0.0%)</t>
+          <t>24 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Porter</t>
+          <t>Physiotherapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>21 (0.0%)</t>
+          <t>24 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Waiting List Manager</t>
+          <t>Intermediate Care staff</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>21 (0.0%)</t>
+          <t>23 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Physiotherapist Consultant</t>
+          <t>Child Protection worker</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>19 (0.0%)</t>
+          <t>22 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Art Therapist Specialist Practitioner</t>
+          <t>Call Operator</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16 (0.0%)</t>
+          <t>21 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Student Nurse - Adult Branch</t>
+          <t>Physician Assistant</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>15 (0.0%)</t>
+          <t>21 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Community Team Manager</t>
+          <t>Porter</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>13 (0.0%)</t>
+          <t>21 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Clinical Team Manager</t>
+          <t>Waiting List Manager</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>12 (0.0%)</t>
+          <t>21 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Art Therapist Consultant</t>
+          <t>Physiotherapist Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>9 (0.0%)</t>
+          <t>19 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Psychotherapist</t>
+          <t>Art Therapist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>9 (0.0%)</t>
+          <t>16 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Student Community Practitioner</t>
+          <t>Student Nurse - Adult Branch</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>9 (0.0%)</t>
+          <t>15 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Clinical Director</t>
+          <t>Community Team Manager</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>8 (0.0%)</t>
+          <t>13 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Clinical Psychologist</t>
+          <t>Clinical Team Manager</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>8 (0.0%)</t>
+          <t>12 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Outpatient Manager</t>
+          <t>Art Therapist Consultant</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>8 (0.0%)</t>
+          <t>9 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>House Officer - Pre Registration</t>
+          <t>Psychotherapist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7 (0.0%)</t>
+          <t>9 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Social Worker</t>
+          <t>Student Community Practitioner</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>7 (0.0%)</t>
+          <t>9 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
+          <t>Clinical Director</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>6 (0.0%)</t>
+          <t>8 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Healthcare Cadet</t>
+          <t>Clinical Psychologist</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>6 (0.0%)</t>
+          <t>8 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Director of Nursing</t>
+          <t>Outpatient Manager</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5 (0.0%)</t>
+          <t>8 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Other Community Health Service - Social Care Worker</t>
+          <t>House Officer - Pre Registration</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5 (0.0%)</t>
+          <t>7 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic, Manager</t>
+          <t>Social Worker</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>5 (0.0%)</t>
+          <t>7 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Midwife</t>
+          <t>Chiropodist/Podiatrist Specialist Practitioner</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>3 (0.0%)</t>
+          <t>6 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Occupational Therapist</t>
+          <t>Healthcare Cadet</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>3 (0.0%)</t>
+          <t>6 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Optometrist</t>
+          <t>Director of Nursing</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>3 (0.0%)</t>
+          <t>5 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Paramedic Consultant</t>
+          <t>Other Community Health Service - Social Care Worker</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>3 (0.0%)</t>
+          <t>5 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Patient Welfare Officer</t>
+          <t>Radiographer - Diagnostic, Manager</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3 (0.0%)</t>
+          <t>5 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Student Physiotherapist</t>
+          <t>Midwife</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Trust Grade Doctor - SHO level</t>
+          <t>Occupational Therapist</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ward Manager</t>
+          <t>Optometrist</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -1919,67 +1919,67 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Audiologist</t>
+          <t>Paramedic Consultant</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2 (0.0%)</t>
+          <t>3 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Chiropodist/Podiatrist Consultant</t>
+          <t>Patient Welfare Officer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2 (0.0%)</t>
+          <t>3 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic, Specialist Practitioner</t>
+          <t>Student Physiotherapist</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2 (0.0%)</t>
+          <t>3 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Specialist Registrar</t>
+          <t>Trust Grade Doctor - SHO level</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2 (0.0%)</t>
+          <t>3 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Technician - Additional Clinical Services</t>
+          <t>Ward Manager</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2 (0.0%)</t>
+          <t>3 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Technician - Healthcare Scientists</t>
+          <t>Audiologist</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Ward Clerk</t>
+          <t>Chiropodist/Podiatrist Consultant</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -2003,67 +2003,67 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Asst. Clinical Medical Officer</t>
+          <t>Radiographer - Diagnostic, Specialist Practitioner</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>1 (0.0%)</t>
+          <t>2 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Biomedical Scientist</t>
+          <t>Specialist Registrar</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>1 (0.0%)</t>
+          <t>2 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Clinical Medical Officer</t>
+          <t>Technician - Additional Clinical Services</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1 (0.0%)</t>
+          <t>2 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Dietitian Manager</t>
+          <t>Technician - Healthcare Scientists</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1 (0.0%)</t>
+          <t>2 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Dietitian Specialist Practitioner</t>
+          <t>Ward Clerk</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1 (0.0%)</t>
+          <t>2 (0.0%)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Multi Therapist Specialist Practitioner</t>
+          <t>Asst. Clinical Medical Officer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Pre-reg Pharmacist</t>
+          <t>Biomedical Scientist</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -2087,7 +2087,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Radiographer - Diagnostic</t>
+          <t>Clinical Medical Officer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -2099,10 +2099,70 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>Dietitian Manager</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>1 (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Dietitian Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>1 (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Multi Therapist Specialist Practitioner</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>1 (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Pre-reg Pharmacist</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>1 (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Radiographer - Diagnostic</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>1 (0.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
           <t>Student District Nurse</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B152" t="inlineStr">
         <is>
           <t>1 (0.0%)</t>
         </is>
